--- a/grupos/3APV - Estadisticos 20211.xlsx
+++ b/grupos/3APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -155,7 +155,7 @@
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Camarillo Aburto Raymundo</t>
+    <t>Martínez Cruz Norma</t>
   </si>
   <si>
     <t>Sánchez Sánchez Miguel</t>
@@ -179,169 +179,169 @@
     <t>BENITEZ</t>
   </si>
   <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>URIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
   </si>
   <si>
     <t>ORTIZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
+    <t>IVETTE</t>
   </si>
   <si>
     <t>JOSE ANTONIO</t>
   </si>
   <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
   </si>
   <si>
     <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
   </si>
 </sst>
 </file>
@@ -845,22 +845,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -887,16 +887,16 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -904,10 +904,10 @@
         <v>13</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -922,13 +922,13 @@
         <v>-1</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -958,10 +958,10 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -999,22 +999,22 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1041,10 +1041,10 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1073,22 +1073,22 @@
         <v>5</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1112,22 +1112,22 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1153,13 +1153,13 @@
         <v>-1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1195,7 +1195,7 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1230,22 +1230,22 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1269,10 +1269,10 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1289,10 +1289,10 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1307,13 +1307,13 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1343,10 +1343,10 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>5</v>
@@ -1384,22 +1384,22 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1426,16 +1426,16 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1461,22 +1461,22 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1538,19 +1538,19 @@
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1580,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1615,19 +1615,19 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1692,22 +1692,22 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1734,16 +1734,16 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1769,22 +1769,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1805,22 +1805,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1846,13 +1846,13 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1882,10 +1882,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1923,22 +1923,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1991,7 +1991,7 @@
         <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2000,22 +2000,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2042,10 +2042,10 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2059,10 +2059,10 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D20">
         <v>5</v>
@@ -2077,13 +2077,13 @@
         <v>-1</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2113,13 +2113,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20">
         <v>-1</v>
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -2154,16 +2154,16 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2193,13 +2193,13 @@
         <v>7</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>5</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2231,13 +2231,13 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2267,7 +2267,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>7</v>
@@ -2308,13 +2308,13 @@
         <v>-1</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2344,13 +2344,13 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>7</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>-1</v>
@@ -2367,10 +2367,10 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D24">
         <v>5</v>
@@ -2385,13 +2385,13 @@
         <v>-1</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2421,13 +2421,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>-1</v>
@@ -2501,19 +2501,19 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>47.62</v>
+        <v>57.14</v>
       </c>
       <c r="G2">
-        <v>47.62</v>
+        <v>38.1</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2533,13 +2533,13 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>52.38</v>
+        <v>57.14</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -2548,10 +2548,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>47.62</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2565,25 +2565,25 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>42.86</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2597,19 +2597,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>57.14</v>
+        <v>76.19</v>
       </c>
       <c r="G5">
-        <v>42.86</v>
+        <v>23.81</v>
       </c>
       <c r="H5">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2629,25 +2629,25 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>90.48</v>
+      </c>
+      <c r="G6">
+        <v>9.52</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>80.95</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.6</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
-      </c>
-      <c r="J6">
-        <v>19.05</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2661,13 +2661,13 @@
         <v>21</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>80.95</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2676,10 +2676,10 @@
         <v>8.6</v>
       </c>
       <c r="I7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>19.05</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2689,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2724,10 +2724,10 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -2744,10 +2744,10 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -2764,10 +2764,10 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -2778,56 +2778,56 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920261</v>
+        <v>20330051920264</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920261</v>
+        <v>20330051920267</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920314</v>
+        <v>20330051920267</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -2838,16 +2838,16 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920264</v>
+        <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -2858,16 +2858,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920267</v>
+        <v>20330051920274</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2878,116 +2878,116 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920267</v>
+        <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
         <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920267</v>
+        <v>20330051920278</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
         <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920267</v>
+        <v>20330051920279</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920270</v>
+        <v>20330051920281</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920274</v>
+        <v>20330051920281</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
         <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920238</v>
+        <v>20330051920282</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -2998,282 +2998,62 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920278</v>
+        <v>20330051920282</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920278</v>
+        <v>19330051920425</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920278</v>
+        <v>19330051920425</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920278</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920279</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920279</v>
-      </c>
-      <c r="B21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920281</v>
-      </c>
-      <c r="B22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920281</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920282</v>
-      </c>
-      <c r="B24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920282</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920425</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>86</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920425</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920425</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>74</v>
-      </c>
-      <c r="D28" t="s">
-        <v>86</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920425</v>
-      </c>
-      <c r="B29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3315,13 +3095,13 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3329,16 +3109,16 @@
         <v>20330051920267</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3346,47 +3126,47 @@
         <v>20330051920278</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920425</v>
+        <v>20330051920281</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920279</v>
+        <v>20330051920282</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -3394,16 +3174,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920281</v>
+        <v>19330051920425</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -3411,33 +3191,33 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920282</v>
+        <v>20330051920264</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920314</v>
+        <v>20330051920270</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3445,16 +3225,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920264</v>
+        <v>20330051920274</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3462,16 +3242,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920270</v>
+        <v>20330051920279</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
         <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -3479,47 +3259,47 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920274</v>
+        <v>20330051920260</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920238</v>
+        <v>19330051920314</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920260</v>
+        <v>20330051920262</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3530,13 +3310,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920262</v>
+        <v>20330051920268</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -3547,13 +3327,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920268</v>
+        <v>20330051920269</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -3564,13 +3344,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920269</v>
+        <v>20330051920271</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
         <v>102</v>
@@ -3581,13 +3361,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920271</v>
+        <v>20330051920272</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -3598,13 +3378,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920272</v>
+        <v>19220030050208</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
         <v>104</v>
@@ -3615,13 +3395,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19220030050208</v>
+        <v>20330051920273</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
@@ -3632,13 +3412,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920273</v>
+        <v>20330051920276</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>106</v>
@@ -3649,13 +3429,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920276</v>
+        <v>19330051920238</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
         <v>107</v>
@@ -3703,16 +3483,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3726,16 +3506,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920314</v>
+        <v>20330051920264</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3749,48 +3529,48 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920268</v>
+        <v>20330051920270</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="s">
-        <v>101</v>
-      </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>19330051920238</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3APV - Estadisticos 20211.xlsx
+++ b/grupos/3APV - Estadisticos 20211.xlsx
@@ -1165,7 +1165,7 @@
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1393,7 +1393,7 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
         <v>8</v>
@@ -1429,7 +1429,7 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1704,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>10</v>
@@ -1740,7 +1740,7 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -2513,7 +2513,7 @@
         <v>38.1</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
         <v>7</v>

--- a/grupos/3APV - Estadisticos 20211.xlsx
+++ b/grupos/3APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -188,154 +188,154 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>AXEL YAEL</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>URIEL ALFREDO</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>ZUNO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
   </si>
   <si>
     <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AXEL YAEL</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>URIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
   </si>
   <si>
     <t>KAREN YAZMIN</t>
@@ -913,7 +913,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>-1</v>
@@ -931,7 +931,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -967,7 +967,7 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -1198,7 +1198,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>5</v>
@@ -1298,7 +1298,7 @@
         <v>5</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1316,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1352,7 +1352,7 @@
         <v>5</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>5</v>
@@ -1837,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -1855,7 +1855,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -1891,7 +1891,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -2068,7 +2068,7 @@
         <v>5</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -2086,7 +2086,7 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2122,7 +2122,7 @@
         <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X20">
         <v>5</v>
@@ -2222,7 +2222,7 @@
         <v>5</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -2240,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2276,7 +2276,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2299,7 +2299,7 @@
         <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -2317,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2353,7 +2353,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X23">
         <v>5</v>
@@ -2376,7 +2376,7 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -2394,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2568,22 +2568,22 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
         <v>66.67</v>
       </c>
       <c r="G4">
+        <v>33.33</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="H4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
       <c r="J4">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -2689,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2724,16 +2724,16 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2744,30 +2744,30 @@
         <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920261</v>
+        <v>20330051920264</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
         <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -2778,16 +2778,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920264</v>
+        <v>20330051920267</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
         <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -2798,33 +2798,33 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920267</v>
+        <v>20330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920267</v>
+        <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
         <v>73</v>
@@ -2838,13 +2838,13 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920270</v>
+        <v>20330051920279</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
         <v>74</v>
@@ -2858,201 +2858,61 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920274</v>
+        <v>20330051920281</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
         <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920278</v>
+        <v>20330051920282</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920278</v>
+        <v>19330051920425</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920279</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920281</v>
-      </c>
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920281</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920282</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920282</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920425</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920425</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3095,112 +2955,112 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920267</v>
+        <v>20330051920264</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920278</v>
+        <v>20330051920267</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920281</v>
+        <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920282</v>
+        <v>20330051920278</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920425</v>
+        <v>20330051920279</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920264</v>
+        <v>20330051920281</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -3208,16 +3068,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920270</v>
+        <v>20330051920282</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -3225,16 +3085,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920274</v>
+        <v>19330051920425</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -3242,30 +3102,30 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920279</v>
+        <v>20330051920260</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920260</v>
+        <v>19330051920314</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
         <v>97</v>
@@ -3276,13 +3136,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920314</v>
+        <v>20330051920262</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
         <v>98</v>
@@ -3293,13 +3153,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920262</v>
+        <v>20330051920268</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3310,13 +3170,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920268</v>
+        <v>20330051920269</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -3327,13 +3187,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920269</v>
+        <v>20330051920271</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -3344,13 +3204,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920271</v>
+        <v>20330051920272</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
         <v>102</v>
@@ -3361,13 +3221,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920272</v>
+        <v>19220030050208</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -3378,13 +3238,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19220030050208</v>
+        <v>20330051920273</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="D19" t="s">
         <v>104</v>
@@ -3395,13 +3255,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920273</v>
+        <v>20330051920274</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
@@ -3415,10 +3275,10 @@
         <v>20330051920276</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
         <v>106</v>
@@ -3432,10 +3292,10 @@
         <v>19330051920238</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
         <v>107</v>
@@ -3489,10 +3349,10 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3512,10 +3372,10 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3535,10 +3395,10 @@
         <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3555,10 +3415,10 @@
         <v>19330051920238</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>107</v>

--- a/grupos/3APV - Estadisticos 20211.xlsx
+++ b/grupos/3APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -146,15 +146,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>Martínez Cruz Norma</t>
   </si>
   <si>
@@ -176,18 +176,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>BENITEZ</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>RAMOS</t>
   </si>
   <si>
@@ -203,18 +233,45 @@
     <t>ZUNO</t>
   </si>
   <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>BAEZ</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>GARNICA</t>
   </si>
   <si>
     <t>ANDRADE</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>CARRASCO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -224,21 +281,54 @@
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>IVETTE</t>
   </si>
   <si>
     <t>ANA KAREN</t>
   </si>
   <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IAN URIEL</t>
+  </si>
+  <si>
     <t>LEONARDO GAEL</t>
   </si>
   <si>
     <t>VALERIA</t>
   </si>
   <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
+    <t>KARLA RENATA</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MIRANDA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>KAREN YAZMIN</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
@@ -252,96 +342,6 @@
   </si>
   <si>
     <t>URIEL ALFREDO</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OJEDA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IAN URIEL</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>KARLA RENATA</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>KAREN YAZMIN</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
 </sst>
 </file>
@@ -863,22 +863,22 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -916,16 +916,16 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -934,46 +934,46 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1017,22 +1017,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1044,7 +1044,7 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1091,28 +1091,28 @@
         <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1121,13 +1121,13 @@
         <v>8</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1150,7 +1150,7 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -1168,43 +1168,43 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <v>6</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1248,22 +1248,22 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1304,13 +1304,13 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1319,46 +1319,46 @@
         <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>5</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1402,22 +1402,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1426,13 +1426,13 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1479,22 +1479,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>10</v>
@@ -1553,25 +1553,25 @@
         <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1589,7 +1589,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1630,25 +1630,25 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1710,22 +1710,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1737,7 +1737,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1787,22 +1787,22 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -1811,7 +1811,7 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1858,46 +1858,46 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>7</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>5</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1941,22 +1941,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1974,7 +1974,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2012,34 +2012,34 @@
         <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2048,10 +2048,10 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2074,7 +2074,7 @@
         <v>5</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -2089,31 +2089,31 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>6</v>
@@ -2125,10 +2125,10 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2151,7 +2151,7 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>7</v>
@@ -2166,46 +2166,46 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2228,7 +2228,7 @@
         <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>7</v>
@@ -2243,37 +2243,37 @@
         <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -2282,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2305,7 +2305,7 @@
         <v>5</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>8</v>
@@ -2320,28 +2320,28 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2350,16 +2350,16 @@
         <v>7</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2382,7 +2382,7 @@
         <v>5</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2397,28 +2397,28 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2430,13 +2430,13 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>42</v>
@@ -2501,30 +2501,30 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>57.14</v>
+        <v>66.67</v>
       </c>
       <c r="G2">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>43</v>
@@ -2533,30 +2533,30 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>57.14</v>
+        <v>76.19</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>23.81</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>44</v>
@@ -2565,19 +2565,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2597,19 +2597,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>76.19</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>23.81</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2629,19 +2629,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>90.48</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>9.52</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2689,7 +2689,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2714,206 +2714,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920261</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920261</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920264</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920267</v>
-      </c>
-      <c r="B5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920270</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920278</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920279</v>
-      </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920281</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920282</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920425</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2949,166 +2749,166 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920261</v>
+        <v>20330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920264</v>
+        <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920267</v>
+        <v>19330051920314</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920262</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920279</v>
+        <v>20330051920267</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920281</v>
+        <v>20330051920268</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920282</v>
+        <v>20330051920269</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920425</v>
+        <v>20330051920270</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920260</v>
+        <v>20330051920271</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
         <v>96</v>
@@ -3119,13 +2919,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920314</v>
+        <v>20330051920272</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>97</v>
@@ -3136,13 +2936,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920262</v>
+        <v>19220030050208</v>
       </c>
       <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
         <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
       </c>
       <c r="D13" t="s">
         <v>98</v>
@@ -3153,13 +2953,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920268</v>
+        <v>20330051920273</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>99</v>
@@ -3170,13 +2970,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920269</v>
+        <v>20330051920274</v>
       </c>
       <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
         <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
       </c>
       <c r="D15" t="s">
         <v>100</v>
@@ -3187,13 +2987,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920271</v>
+        <v>20330051920276</v>
       </c>
       <c r="B16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
         <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>101</v>
@@ -3204,13 +3004,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920272</v>
+        <v>19330051920238</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
         <v>102</v>
@@ -3221,13 +3021,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19220030050208</v>
+        <v>20330051920278</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D18" t="s">
         <v>103</v>
@@ -3238,13 +3038,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920273</v>
+        <v>20330051920279</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
         <v>104</v>
@@ -3255,13 +3055,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920274</v>
+        <v>20330051920281</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
         <v>105</v>
@@ -3272,13 +3072,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920276</v>
+        <v>20330051920282</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
         <v>106</v>
@@ -3289,13 +3089,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920238</v>
+        <v>19330051920425</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
         <v>107</v>
@@ -3311,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3343,22 +3143,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920264</v>
+        <v>20330051920261</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3366,70 +3166,254 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920264</v>
+        <v>20330051920261</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>20330051920267</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>43</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920238</v>
+        <v>20330051920267</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>42</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920278</v>
+      </c>
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920278</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920281</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920281</v>
+      </c>
+      <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920264</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920274</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920282</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920425</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3APV - Estadisticos 20211.xlsx
+++ b/grupos/3APV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="108">
   <si>
     <t>Materia</t>
   </si>
@@ -952,7 +952,7 @@
         <v>5</v>
       </c>
       <c r="R5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -1183,7 +1183,7 @@
         <v>6</v>
       </c>
       <c r="R8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1201,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="R17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>5</v>
@@ -1894,7 +1894,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2030,7 +2030,7 @@
         <v>9</v>
       </c>
       <c r="R19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>5</v>
@@ -2048,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2261,7 +2261,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -2279,7 +2279,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2415,7 +2415,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S24">
         <v>0</v>
@@ -2433,7 +2433,7 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2565,19 +2565,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3111,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3327,22 +3327,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920264</v>
+        <v>19330051920425</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920274</v>
+        <v>19330051920425</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -3373,16 +3373,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920282</v>
+        <v>20330051920264</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -3396,24 +3396,47 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920425</v>
+        <v>20330051920274</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920282</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
         <v>42</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>5</v>
       </c>
     </row>
